--- a/artfynd/A 8663-2022 artfynd.xlsx
+++ b/artfynd/A 8663-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 8663-2022 artfynd.xlsx
+++ b/artfynd/A 8663-2022 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>7032023</v>
+        <v>80043240</v>
       </c>
       <c r="B2" t="n">
-        <v>90008</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>96458</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,47 +686,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6031</v>
+        <v>2818</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Brid.) Z.Iwats.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Skogen ost Brobystugan, Srm</t>
+          <t>Runtuna, Nyköpings kommun, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>619270.1106143877</v>
+        <v>618941</v>
       </c>
       <c r="R2" t="n">
-        <v>6524920.259209079</v>
+        <v>6524715</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -755,22 +742,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2013-11-10</t>
+          <t>2019-09-22</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2013-11-10</t>
+          <t>2019-09-22</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -779,71 +766,66 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Per Skyllberg</t>
+          <t>Amanda Lidén</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Per Skyllberg</t>
+          <t>Amanda Lidén</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>80043240</v>
+        <v>80045234</v>
       </c>
       <c r="B3" t="n">
-        <v>93158</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2818</v>
+        <v>4361</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Runtuna, Nyköpings kommun, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>618941.3277256249</v>
+        <v>618941</v>
       </c>
       <c r="R3" t="n">
-        <v>6524715.426091342</v>
+        <v>6524715</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -873,27 +855,18 @@
           <t>2019-09-22</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>16:26</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2019-09-22</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>16:26</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -915,16 +888,11 @@
         <v>80045315</v>
       </c>
       <c r="B4" t="n">
-        <v>90674</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93233</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -937,12 +905,12 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -955,10 +923,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>618941.3277256249</v>
+        <v>618941</v>
       </c>
       <c r="R4" t="n">
-        <v>6524715.426091342</v>
+        <v>6524715</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -988,19 +956,9 @@
           <t>2019-09-22</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2019-09-22</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1028,56 +986,58 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>80045234</v>
+        <v>7032023</v>
       </c>
       <c r="B5" t="n">
-        <v>90645</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92567</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4361</v>
+        <v>6031</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+          <t>(Wulfen:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Runtuna, Nyköpings kommun, Srm</t>
+          <t>Skogen ost Brobystugan, Srm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>618941.3277256249</v>
+        <v>619270</v>
       </c>
       <c r="R5" t="n">
-        <v>6524715.426091342</v>
+        <v>6524920</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1101,22 +1061,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2019-09-22</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2013-11-10</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2019-09-22</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2013-11-10</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1132,12 +1082,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Amanda Lidén</t>
+          <t>Per Skyllberg</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Amanda Lidén</t>
+          <t>Per Skyllberg</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>

--- a/artfynd/A 8663-2022 artfynd.xlsx
+++ b/artfynd/A 8663-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -781,6 +786,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80043240</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -882,6 +892,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80045234</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -983,6 +998,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80045315</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1091,8 +1111,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/7032023</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>